--- a/full_detailed_aggregated_report_ten_west.xlsx
+++ b/full_detailed_aggregated_report_ten_west.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI Company\AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tlbbs\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916E4EBA-CE50-499A-9A61-EC129BFE0203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22FE334-0B5C-43D8-953D-28F18272B52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7288" uniqueCount="2118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7298" uniqueCount="2118">
   <si>
     <t>GM</t>
   </si>
@@ -16228,6 +16228,9 @@
       <c r="P140" t="s">
         <v>27</v>
       </c>
+      <c r="R140" t="s">
+        <v>27</v>
+      </c>
       <c r="S140" t="s">
         <v>28</v>
       </c>
@@ -18114,6 +18117,9 @@
       <c r="P168" t="s">
         <v>27</v>
       </c>
+      <c r="R168" t="s">
+        <v>27</v>
+      </c>
       <c r="S168" t="s">
         <v>28</v>
       </c>
@@ -27616,6 +27622,9 @@
       <c r="P308" t="s">
         <v>27</v>
       </c>
+      <c r="R308" t="s">
+        <v>27</v>
+      </c>
       <c r="S308" t="s">
         <v>28</v>
       </c>
@@ -28618,6 +28627,9 @@
       <c r="P323" t="s">
         <v>27</v>
       </c>
+      <c r="R323" t="s">
+        <v>27</v>
+      </c>
       <c r="S323" t="s">
         <v>28</v>
       </c>
@@ -28668,6 +28680,9 @@
       <c r="P324" t="s">
         <v>27</v>
       </c>
+      <c r="R324" t="s">
+        <v>27</v>
+      </c>
       <c r="S324" t="s">
         <v>28</v>
       </c>
@@ -28922,6 +28937,9 @@
       <c r="P328" t="s">
         <v>27</v>
       </c>
+      <c r="R328" t="s">
+        <v>27</v>
+      </c>
       <c r="S328" t="s">
         <v>28</v>
       </c>
@@ -29108,6 +29126,9 @@
       <c r="P331" t="s">
         <v>27</v>
       </c>
+      <c r="R331" t="s">
+        <v>27</v>
+      </c>
       <c r="S331" t="s">
         <v>28</v>
       </c>
@@ -29158,6 +29179,9 @@
       <c r="P332" t="s">
         <v>27</v>
       </c>
+      <c r="R332" t="s">
+        <v>27</v>
+      </c>
       <c r="S332" t="s">
         <v>28</v>
       </c>
@@ -29208,6 +29232,9 @@
       <c r="P333" t="s">
         <v>27</v>
       </c>
+      <c r="R333" t="s">
+        <v>27</v>
+      </c>
       <c r="S333" t="s">
         <v>28</v>
       </c>
@@ -29256,6 +29283,9 @@
         <v>27</v>
       </c>
       <c r="P334" t="s">
+        <v>27</v>
+      </c>
+      <c r="R334" t="s">
         <v>27</v>
       </c>
       <c r="S334" t="s">
